--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_02_20_Cau.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -639,7 +639,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hình dung tổng xác suất tích lũy sẽ đạt ngưỡng sớm hay muộn khi top-p nhỏ đi.</t>
+          <t>Khi giảm top-p từ 0,95 xuống 0,60, tổng xác suất tích lũy của các token có xác suất cao nhất đạt ngưỡng 0,60 sớm hơn, khiến tập token ứng viên được giữ lại trở nên hẹp hơn.</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -685,7 +685,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chia ngân sách đầu ra cho số bản tóm tắt độc lập.</t>
+          <t>Ngân sách tối đa 2.400 token đầu ra chia đều cho 12 bản tóm tắt độc lập: 2.400 / 12 = 200 token cho mỗi bản.</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -731,7 +731,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt cấu hình trước khi gọi với thông tin cho biết lý do dừng sau khi nhận phản hồi.</t>
+          <t>Khi đặt `max_output_tokens=120` và phản hồi bị dừng giữa câu, có thể mô hình đã chạm giới hạn đầu ra; cần kiểm tra `finish_reason` trong phản hồi (nếu là 'length' thì khẳng định bị cắt do hết token).</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cộng mọi thành phần trước rồi lấy dung lượng cửa sổ trừ đi tổng đó.</t>
+          <t>Tổng số token đã phân bổ gồm lời nhắc (2.500), lịch sử hội thoại (8.500), ngữ cảnh truy xuất (12.000) và giới hạn đầu ra (6.000) là: 2.500 + 8.500 + 12.000 + 6.000 = 29.000 token. Số token còn dư trong cửa sổ ngữ cảnh 32.000 là: 32.000 - 29.000 = 3.000 token.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -876,7 +876,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính phần vượt trước, rồi loại các phương án làm mất phần bằng chứng phải giữ.</t>
+          <t>Tổng ngân sách hiện tại = 2.000 (prompt) + 6.000 (history) + 7.000 (evidence) + 4.000 (output) = 19.000 token, vượt cửa sổ 16.000 là 3.000 token. Giảm giới hạn đầu ra 2.000 token và tóm tắt giảm lịch sử 1.000 token giúp giảm đúng 3.000 token vừa vặn cửa sổ mà vẫn giữ nguyên bằng chứng 7.000.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -968,7 +968,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm dấu hiệu cho thấy câu trả lời có thể đã thay đổi sau thời điểm mô hình được huấn luyện.</t>
+          <t>Giá API và endpoint thay đổi theo thời gian thực và không thể trả lời chính xác từ trí nhớ tĩnh của mô hình; cách xử lý đúng là tra cứu tài liệu chính thức hiện hành hoặc gọi tool tìm kiếm và ghi rõ mốc thời gian kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-B, 2-C, 3-A</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1076,7 +1076,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm đơn vị rời rạc hoặc từng đoạn mà mô hình xử lý sau bước tiền xử lý.</t>
+          <t>Văn bản (x1) biểu diễn bằng mảnh từ hoặc mã định danh token (r1); Hình ảnh (x2) biểu diễn bằng mảnh ảnh (image patches) hoặc token hình ảnh (r2); Âm thanh (x3) biểu diễn bằng khung/đoạn âm thanh được mã hóa thành token (r3).</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1178,7 +1178,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ kết luận trong đúng phạm vi và đúng loại cơ chế đã được đo.</t>
+          <t>Các thí nghiệm probe và can thiệp trên mô hình Othello chỉ chứng minh mô hình học được biểu diễn nội tại về trạng thái bàn cờ của trò chơi đó. Kết luận 'Mô hình đã có hiểu biết có ý thức và world model tổng quát cho mọi lĩnh vực' vượt quá bằng chứng thu được nhiều nhất.</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1270,7 +1270,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cùng danh tính token nhưng vai trò có thể thay đổi theo vị trí trong câu.</t>
+          <t>Kiến trúc Transformer xử lý các token song song và có tính bất biến với thứ tự (permutation invariant); positional encoding bổ sung thông tin vị trí vào vector biểu diễn để attention phân biệt được trật tự từ ('chó cắn mèo' khác 'mèo cắn chó').</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o4 → o2 → o1 → o3</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1322,7 +1322,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Attention cần nhận biểu diễn đã mang cả danh tính token và vị trí.</t>
+          <t>Luồng đầu vào Transformer trước khối attention gồm: tách văn bản thành token IDs (o4) -&gt; tra token embedding từ token IDs (o2) -&gt; cộng hoặc kết hợp thông tin vị trí positional encoding (o1) -&gt; đưa biểu diễn vào khối attention (o3).</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1470,7 +1470,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ kết luận trong đúng head, đúng tầng và đúng ba token được quan sát.</t>
+          <t>Trọng số attention 0,62 tới `river` cho thấy trong head và tầng cụ thể này, biểu diễn của token `bank` nhận được đóng góp lớn nhất từ token `river` trong số ba token được quan sát.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1565,7 +1565,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh dữ liệu có sẵn ở bước huấn luyện với dữ liệu thật sự có khi sinh tuần tự.</t>
+          <t>Khi dự đoán token ở vị trí 5, việc che token ở vị trí 6 (causal mask) là bắt buộc vì nếu cho phép nhìn thấy vị trí 6, mô hình sẽ bị rò rỉ thông tin tương lai - điều không thể xảy ra khi sinh văn bản tự hồi quy ở thời điểm suy luận.</t>
         </is>
       </c>
     </row>
